--- a/www/ig/fhir/ror/ValueSet-ror-usage-context-type-vs.xlsx
+++ b/www/ig/fhir/ror/ValueSet-ror-usage-context-type-vs.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -46,7 +46,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Value Set type pour le contexte d'usage de la fiche de saisie</t>
+    <t>Value Set type pour le contexte d'usage du modèle de saisie</t>
   </si>
   <si>
     <t>Status</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T09:54:01+00:00</t>
+    <t>2026-04-29T15:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,13 +82,13 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Extension du Value Set http://hl7.org/fhir/ValueSet/usage-context-type pour fixer le type de contexte d'usage de la fiche de saisie avec le code EG ou le S pour Spécialité ordinale ou P01 pour le type de profession</t>
+    <t>Extension du Value Set http://hl7.org/fhir/ValueSet/usage-context-type pour fixer le type de contexte d'usage du modèle de saisie avec le code EG ou le S pour Spécialité ordinale ou P01 pour le type de profession</t>
   </si>
   <si>
     <t>Purpose</t>
